--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2017/WISCONSIN_2017.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2017/WISCONSIN_2017.xlsx
@@ -1878,7 +1878,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Cuatro Cienegas</t>
+          <t>Cuatrocienegas</t>
         </is>
       </c>
       <c r="C85">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C232">
@@ -11976,7 +11976,7 @@
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C646">
@@ -11994,7 +11994,7 @@
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 26 -</t>
+          <t>San Juan Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C647">
